--- a/VerveStacks_JOR/vt_vervestacks_JOR_v1.xlsx
+++ b/VerveStacks_JOR/vt_vervestacks_JOR_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2065B303-D7F9-4F50-A848-793236DCC15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFD0D0F4-19B4-4D97-BEAD-FE3FB56ABC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00C6046A-AEE3-43E1-A1F9-C9ABD9ADB444}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0397A3E0-BCB0-4A94-ABCC-9D5B2C83A368}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -832,7 +832,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64824A8A-E05F-414D-A614-2652054DB6F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04364536-8305-418F-AE6B-4885B790F844}">
   <dimension ref="B9:T26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -911,7 +911,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.47197499999999998</v>
+        <v>0.32094299999999998</v>
       </c>
       <c r="F11">
         <v>1365</v>
@@ -967,7 +967,7 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.44349375000000002</v>
+        <v>0.30157575000000003</v>
       </c>
       <c r="F12">
         <v>1365</v>
@@ -1023,7 +1023,7 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0.42315000000000003</v>
+        <v>0.28774200000000005</v>
       </c>
       <c r="F13">
         <v>1365</v>
@@ -1079,7 +1079,7 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.42315000000000003</v>
+        <v>0.28774200000000005</v>
       </c>
       <c r="F14">
         <v>1365</v>
@@ -1135,7 +1135,7 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.42315000000000003</v>
+        <v>0.28774200000000005</v>
       </c>
       <c r="F15">
         <v>1365</v>
@@ -1191,7 +1191,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.47197499999999998</v>
+        <v>0.32094300000000003</v>
       </c>
       <c r="F16">
         <v>1365</v>
@@ -1247,7 +1247,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.45569999999999999</v>
+        <v>0.3098760000000001</v>
       </c>
       <c r="F17">
         <v>1365</v>
@@ -1303,7 +1303,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.47197499999999998</v>
+        <v>0.32094300000000003</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -1359,7 +1359,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.28888124999999998</v>
+        <v>0.19643924999999998</v>
       </c>
       <c r="F19">
         <v>1365</v>
@@ -1415,7 +1415,7 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.28888124999999998</v>
+        <v>0.19643924999999998</v>
       </c>
       <c r="F20">
         <v>1365</v>
@@ -1471,7 +1471,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.26853750000000004</v>
+        <v>0.18260550000000003</v>
       </c>
       <c r="F21">
         <v>1365</v>
@@ -1527,7 +1527,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.26853750000000004</v>
+        <v>0.18260550000000003</v>
       </c>
       <c r="F22">
         <v>1365</v>
@@ -1583,7 +1583,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>0.26853750000000004</v>
+        <v>0.18260550000000003</v>
       </c>
       <c r="F23">
         <v>1365</v>
@@ -1639,7 +1639,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.28481250000000008</v>
+        <v>0.19367250000000003</v>
       </c>
       <c r="F24">
         <v>1365</v>
@@ -1695,7 +1695,7 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.27260625000000005</v>
+        <v>0.18537225000000002</v>
       </c>
       <c r="F25">
         <v>1365</v>
@@ -1751,7 +1751,7 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.27260625000000005</v>
+        <v>0.18537225000000002</v>
       </c>
       <c r="F26">
         <v>1365</v>
@@ -1802,7 +1802,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F3E9119-F5DC-409C-B08F-5DA9B1F73780}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7B6D3F2-F32B-4972-B7FB-22F548F16D96}">
   <dimension ref="B9:T13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2038,7 +2038,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1500A2B0-B788-4C8A-BD7B-09E0A56397D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D9B4EB-E6C2-4C15-BCDA-55ACF40D867F}">
   <dimension ref="B9:T77"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2123,7 +2123,7 @@
         <v>0.01</v>
       </c>
       <c r="G11">
-        <v>0.29760000000000003</v>
+        <v>0.20236800000000005</v>
       </c>
       <c r="H11">
         <v>4252.5</v>
@@ -2176,7 +2176,7 @@
         <v>0.373</v>
       </c>
       <c r="G12">
-        <v>0.53939999999999999</v>
+        <v>0.36679199999999995</v>
       </c>
       <c r="H12">
         <v>900</v>
@@ -2229,7 +2229,7 @@
         <v>0.4</v>
       </c>
       <c r="G13">
-        <v>0.50685000000000002</v>
+        <v>0.34465800000000002</v>
       </c>
       <c r="H13">
         <v>900</v>
@@ -2282,7 +2282,7 @@
         <v>0.3</v>
       </c>
       <c r="G14">
-        <v>0.48360000000000003</v>
+        <v>0.32884800000000003</v>
       </c>
       <c r="H14">
         <v>1035</v>
@@ -2335,7 +2335,7 @@
         <v>0.3</v>
       </c>
       <c r="G15">
-        <v>0.48360000000000003</v>
+        <v>0.32884800000000003</v>
       </c>
       <c r="H15">
         <v>1035</v>
@@ -2388,7 +2388,7 @@
         <v>0.3</v>
       </c>
       <c r="G16">
-        <v>0.48360000000000003</v>
+        <v>0.32884800000000003</v>
       </c>
       <c r="H16">
         <v>1035</v>
@@ -2441,7 +2441,7 @@
         <v>0.42899999999999999</v>
       </c>
       <c r="G17">
-        <v>0.53939999999999999</v>
+        <v>0.36679200000000001</v>
       </c>
       <c r="H17">
         <v>900</v>
@@ -2494,7 +2494,7 @@
         <v>0.21199999999999999</v>
       </c>
       <c r="G18">
-        <v>0.52080000000000004</v>
+        <v>0.35414400000000007</v>
       </c>
       <c r="H18">
         <v>1035</v>
@@ -2547,7 +2547,7 @@
         <v>0.48499999999999999</v>
       </c>
       <c r="G19">
-        <v>0.53939999999999999</v>
+        <v>0.36679200000000001</v>
       </c>
       <c r="H19">
         <v>900</v>
@@ -2600,7 +2600,7 @@
         <v>0.24</v>
       </c>
       <c r="G20">
-        <v>0.33015</v>
+        <v>0.22450200000000001</v>
       </c>
       <c r="H20">
         <v>1138.5</v>
@@ -2653,7 +2653,7 @@
         <v>0.57379999999999998</v>
       </c>
       <c r="G21">
-        <v>0.33015</v>
+        <v>0.22450199999999998</v>
       </c>
       <c r="H21">
         <v>990.00000000000011</v>
@@ -2706,7 +2706,7 @@
         <v>0.13</v>
       </c>
       <c r="G22">
-        <v>0.30690000000000001</v>
+        <v>0.20869200000000002</v>
       </c>
       <c r="H22">
         <v>1242</v>
@@ -2759,7 +2759,7 @@
         <v>0.13</v>
       </c>
       <c r="G23">
-        <v>0.30690000000000001</v>
+        <v>0.20869200000000002</v>
       </c>
       <c r="H23">
         <v>1242</v>
@@ -2812,7 +2812,7 @@
         <v>0.13</v>
       </c>
       <c r="G24">
-        <v>0.30690000000000001</v>
+        <v>0.20869200000000002</v>
       </c>
       <c r="H24">
         <v>1242</v>
@@ -2909,7 +2909,7 @@
         <v>0.05</v>
       </c>
       <c r="G26">
-        <v>0.32550000000000007</v>
+        <v>0.22134000000000004</v>
       </c>
       <c r="H26">
         <v>1215</v>
@@ -2962,7 +2962,7 @@
         <v>0.23499999999999999</v>
       </c>
       <c r="G27">
-        <v>0.31155000000000005</v>
+        <v>0.21185400000000004</v>
       </c>
       <c r="H27">
         <v>1345.4999999999998</v>
@@ -3015,7 +3015,7 @@
         <v>0.23499999999999999</v>
       </c>
       <c r="G28">
-        <v>0.31155000000000005</v>
+        <v>0.21185400000000004</v>
       </c>
       <c r="H28">
         <v>1345.4999999999998</v>
@@ -3074,7 +3074,7 @@
         <v>33</v>
       </c>
       <c r="L29">
-        <v>0.26987662184873007</v>
+        <v>0.26987662184873001</v>
       </c>
       <c r="N29" t="s">
         <v>71</v>
@@ -3121,7 +3121,7 @@
         <v>33</v>
       </c>
       <c r="L30">
-        <v>0.26987662184873007</v>
+        <v>0.26987662184873001</v>
       </c>
       <c r="N30" t="s">
         <v>71</v>
@@ -3168,7 +3168,7 @@
         <v>33</v>
       </c>
       <c r="L31">
-        <v>0.26987662184873007</v>
+        <v>0.26987662184873001</v>
       </c>
       <c r="N31" t="s">
         <v>71</v>
@@ -5033,7 +5033,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E906325D-8921-4B63-BD34-E44CC6E65B13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7681DA1D-0A63-4392-9014-DE2FCFCAA7ED}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
